--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -51,945 +51,948 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="324">
-  <si>
-    <t xml:space="preserve">asura title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asura id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flame title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flame id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tapas title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tapas id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vortex title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vortex id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">webtoon title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">webtoon id</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
+  <si>
+    <t>asura_title</t>
+  </si>
+  <si>
+    <t>asura_id</t>
+  </si>
+  <si>
+    <t>flame_title</t>
+  </si>
+  <si>
+    <t>flame_id</t>
+  </si>
+  <si>
+    <t>tapas_title</t>
+  </si>
+  <si>
+    <t>tapas_id</t>
+  </si>
+  <si>
+    <t>vortex_title</t>
+  </si>
+  <si>
+    <t>vortex_id</t>
+  </si>
+  <si>
+    <t>webtoon_title</t>
+  </si>
+  <si>
+    <t>webtoon_id</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academy's Genius Swordmaster</t>
+  </si>
+  <si>
+    <t>academys-genius-swordmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academy's Genius Swordsman</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>asura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damn Reincarnation</t>
+  </si>
+  <si>
+    <t>damn-reincarnation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragon-Devouring Mage</t>
+  </si>
+  <si>
+    <t>dragon-devouring-mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duke Pendragon</t>
+  </si>
+  <si>
+    <t>duke-pendragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Odyssey</t>
+  </si>
+  <si>
+    <t>dungeon-odyssey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helmut: The Forsaken Child</t>
+  </si>
+  <si>
+    <t>helmut-the-forsaken-child</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinite Mage</t>
+  </si>
+  <si>
+    <t>infinite-mage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logging 10,000 Years into the Future</t>
+  </si>
+  <si>
+    <t>logging-10000-years-into-the-future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martial God Regressed to Level 2</t>
+  </si>
+  <si>
+    <t>martial-god-regressed-to-level-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The God of War Who Regressed to Level 2</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim Login</t>
+  </si>
+  <si>
+    <t>murim-login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nano Machine</t>
+  </si>
+  <si>
+    <t>nano-machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Necromancer's Evolutionary Traits</t>
+  </si>
+  <si>
+    <t>necromancers-evolutionary-traits</t>
+  </si>
+  <si>
+    <t>Overgeared</t>
+  </si>
+  <si>
+    <t>overgeared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overpowered Sword</t>
+  </si>
+  <si>
+    <t>overpowered-sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick Me Up, Infinite Gacha</t>
+  </si>
+  <si>
+    <t>pick-me-up-infinite-gacha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player Who Can't Level Up</t>
+  </si>
+  <si>
+    <t>player-who-cant-level-up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player Who Returned 10,000 Years Later</t>
+  </si>
+  <si>
+    <t>player-who-returned-10000-years-later</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Disaster-Class Hero</t>
+  </si>
+  <si>
+    <t>return-of-the-disaster-class-hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Of The Shattered Constellation</t>
+  </si>
+  <si>
+    <t>return-of-the-shattered-constellation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Broken Constellation</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge of the Iron-Blooded Sword Hound</t>
+  </si>
+  <si>
+    <t>revenge-of-the-iron-blooded-sword-hound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Leveling: Ragnarok</t>
+  </si>
+  <si>
+    <t>solo-leveling-ragnarok</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Max-Level Newbie</t>
+  </si>
+  <si>
+    <t>solo-max-level-newbie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard of Reincarnation</t>
+  </si>
+  <si>
+    <t>standard-of-reincarnation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swordmaster’s Youngest Son</t>
+  </si>
+  <si>
+    <t>swordmasters-youngest-son</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent-Swallowing Magician</t>
+  </si>
+  <si>
+    <t>talent-swallowing-magician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Great Mage Returns After 4000 Years</t>
+  </si>
+  <si>
+    <t>the-great-mage-returns-after-4000-years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Heavenly Demon Can't Live a Normal Life</t>
+  </si>
+  <si>
+    <t>the-heavenly-demon-cant-live-a-normal-life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hero Returns</t>
+  </si>
+  <si>
+    <t>the-hero-returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Indomitable Martial King</t>
+  </si>
+  <si>
+    <t>the-indomitable-martial-king</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Slip of the Fist King</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Player Hides His Past</t>
+  </si>
+  <si>
+    <t>the-player-hides-his-past</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Tutorial is Too Hard</t>
+  </si>
+  <si>
+    <t>the-tutorial-is-too-hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wandering Warrior of Wudang</t>
+  </si>
+  <si>
+    <t>wandering-warrior-of-wudang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Youngest Scion of the Mages</t>
+  </si>
+  <si>
+    <t>youngest-scion-of-the-mages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Talent is Mine</t>
+  </si>
+  <si>
+    <t>your-talent-is-mine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BJ Archmage</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>flame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon Reset</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRL Quest</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Job Change: I'm Stuck As the Weakest Dragon Tamer?!</t>
+  </si>
+  <si>
+    <t>323478</t>
+  </si>
+  <si>
+    <t>tapas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leveling with the Gods</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leveling up with Gods</t>
+  </si>
+  <si>
+    <t>leveling-up-with-gods</t>
+  </si>
+  <si>
+    <t>vortex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing as the Reincarnated Bastard of the Sword Clan</t>
+  </si>
+  <si>
+    <t>154</t>
+  </si>
+  <si>
+    <t>regressing-as-the-reincarnated-bastard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of The Frozen Player</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Frozen Player Returns</t>
+  </si>
+  <si>
+    <t>the-frozen-player-returns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evolution: Road to Space Monster</t>
+  </si>
+  <si>
+    <t>evolution-road-to-space-monster-m3jhpw3j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Became a Renowned Family’s Sword Prodigy</t>
+  </si>
+  <si>
+    <t>i-became-a-renowned-family's-sword-prodigy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kill The Dragon</t>
+  </si>
+  <si>
+    <t>kill-the-dragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maxed Out Leveling</t>
+  </si>
+  <si>
+    <t>maxed-out-leveling2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranker's Return</t>
+  </si>
+  <si>
+    <t>rankers-return-c6f3k3os</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latna Saga: Survival of a Sword King</t>
+  </si>
+  <si>
+    <t>193936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survival Story of a Sword King in a Fantasy World</t>
+  </si>
+  <si>
+    <t>survival-story-of-a-sword-king-in-a-fantasy-world</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Beginning After the End</t>
+  </si>
+  <si>
+    <t>the-beginning-after-the-end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Druid of Seoul Station</t>
+  </si>
+  <si>
+    <t>the-druid-of-seoul-station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Lord of Coins</t>
+  </si>
+  <si>
+    <t>the-lord-of-coins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Skeleton Soldier Failed to Defend the Dungeon</t>
+  </si>
+  <si>
+    <t>the-skeleton-soldier-failed-to-defend-the-dungeon-0ky1nyb0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Worn and Torn Newbie</t>
+  </si>
+  <si>
+    <t>the-worn-and-torn-newbie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zig the Blacksmith</t>
+  </si>
+  <si>
+    <t>zig-the-blacksmith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Regression</t>
+  </si>
+  <si>
+    <t>absolute-regression</t>
+  </si>
+  <si>
+    <t>7004</t>
+  </si>
+  <si>
+    <t>webtoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academy's Undercover Professor</t>
+  </si>
+  <si>
+    <t>academys-undercover-professor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Academy's Undercover Professor</t>
+  </si>
+  <si>
+    <t>4636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bad Born Blood</t>
+  </si>
+  <si>
+    <t>bad-born-blood</t>
+  </si>
+  <si>
+    <t>7208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundless Necromancer</t>
+  </si>
+  <si>
+    <t>boundless-necromancer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boundless Ascension</t>
+  </si>
+  <si>
+    <t>5228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eternally Regressing Knight</t>
+  </si>
+  <si>
+    <t>eternally-regressing-knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Knight Only Lives Today</t>
+  </si>
+  <si>
+    <t>6672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genius of the Unique Lineage</t>
+  </si>
+  <si>
+    <t>genius-of-the-unique-lineage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Perfect Hybrid</t>
+  </si>
+  <si>
+    <t>5050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Obtained a Mythic Item</t>
+  </si>
+  <si>
+    <t>i-obtained-a-mythic-item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mythic Item Obtained</t>
+  </si>
+  <si>
+    <t>4582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omniscient Reader’s Viewpoint</t>
+  </si>
+  <si>
+    <t>omniscient-readers-viewpoint</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omniscient Reader</t>
+  </si>
+  <si>
+    <t>2154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reformation of the Deadbeat Noble</t>
+  </si>
+  <si>
+    <t>reformation-of-the-deadbeat-noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Lazy Lord Masters the Sword</t>
+  </si>
+  <si>
+    <t>3349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regressing with the King’s Power</t>
+  </si>
+  <si>
+    <t>regressing-with-the-kings-power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returned by the King</t>
+  </si>
+  <si>
+    <t>6213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reincarnation of the Suicidal Battle God</t>
+  </si>
+  <si>
+    <t>reincarnation-of-the-suicidal-battle-god</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doom Breaker</t>
+  </si>
+  <si>
+    <t>3197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Mount Hua Sect</t>
+  </si>
+  <si>
+    <t>return-of-the-mount-hua-sect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return of the Blossoming Blade</t>
+  </si>
+  <si>
+    <t>2849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star Instructor, Master Baek</t>
+  </si>
+  <si>
+    <t>star-instructor-master-baek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best Teacher Baek</t>
+  </si>
+  <si>
+    <t>4153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star-Embracing Swordmaster</t>
+  </si>
+  <si>
+    <t>star-embracing-swordmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star-Fostered Swordmaster</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Stellar Swordmaster</t>
+  </si>
+  <si>
+    <t>5988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel-Eating Player</t>
+  </si>
+  <si>
+    <t>steel-eating-player</t>
+  </si>
+  <si>
+    <t>5966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surviving the Game as a Barbarian</t>
+  </si>
+  <si>
+    <t>surviving-the-game-as-a-barbarian</t>
+  </si>
+  <si>
+    <t>5515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sword Fanatic Wanders Through The Night</t>
+  </si>
+  <si>
+    <t>sword-fanatic-wanders-through-the-night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the Night Consumed by Blades, I Walk</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Dance of Swords in the Night</t>
+  </si>
+  <si>
+    <t>4596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Dark Magician Transmigrates After 66666 Years</t>
+  </si>
+  <si>
+    <t>the-dark-magician-transmigrates-after-66666-years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66,666 Years: Advent of the Dark Mage</t>
+  </si>
+  <si>
+    <t>3441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Extra’s Academy Survival Guide</t>
+  </si>
+  <si>
+    <t>the-extras-academy-survival-guide</t>
+  </si>
+  <si>
+    <t>6465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Greatest Estate Developer</t>
+  </si>
+  <si>
+    <t>the-greatest-estate-developer</t>
+  </si>
+  <si>
+    <t>3596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressed Son of a Duke is an Assassin</t>
+  </si>
+  <si>
+    <t>the-regressed-son-of-a-duke-is-an-assassin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Regressed Youngest Son of the Duke is an Assassin</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reborn Young Lord is an Assassin</t>
+  </si>
+  <si>
+    <t>6107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villain to Kill</t>
+  </si>
+  <si>
+    <t>villain-to-kill</t>
+  </si>
+  <si>
+    <t>2857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Demon Cultivation Simulation</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murim RPG Simulation</t>
+  </si>
+  <si>
+    <t>murim-rpg-simulation-jdjd0y0v</t>
+  </si>
+  <si>
+    <t>3779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jungle Juice</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>jungle-juice</t>
+  </si>
+  <si>
+    <t>2480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo Necromancy</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Lone Necromancer</t>
+  </si>
+  <si>
+    <t>3690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Dungeon Cleaning Life of a Once Genius Hunter</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>4677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster Eater</t>
+  </si>
+  <si>
+    <t>monster-eater</t>
+  </si>
+  <si>
+    <t>7363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regression of the Close Combat Mage</t>
+  </si>
+  <si>
+    <t>regression-of-the-close-combat-mage</t>
+  </si>
+  <si>
+    <t>6780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return to Player</t>
+  </si>
+  <si>
+    <t>return-to-player</t>
+  </si>
+  <si>
+    <t>2574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower of God: Urek Mazino</t>
+  </si>
+  <si>
+    <t>tog-urek-mazino</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower of God</t>
+  </si>
+  <si>
+    <t>Eleceed</t>
+  </si>
+  <si>
+    <t>1571</t>
+  </si>
+  <si>
+    <t>Deor</t>
+  </si>
+  <si>
+    <t>1663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My S-Class Hunters</t>
+  </si>
+  <si>
+    <t>3963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Was the Final Boss</t>
+  </si>
+  <si>
+    <t>5170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lord of Goblins</t>
+  </si>
+  <si>
+    <t>5227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Hammer</t>
+  </si>
+  <si>
+    <t>5382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrolling in the Transcendent Academy</t>
+  </si>
+  <si>
+    <t>5420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Becoming the Monarch</t>
+  </si>
+  <si>
+    <t>5549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time-Limited Genius Dark Knight</t>
+  </si>
+  <si>
+    <t>5639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Night of the Goblin</t>
+  </si>
+  <si>
+    <t>5986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Last Adventurer</t>
+  </si>
+  <si>
+    <t>6135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supremely Talented Player</t>
+  </si>
+  <si>
+    <t>6215</t>
+  </si>
+  <si>
+    <t>Reincarnator</t>
+  </si>
+  <si>
+    <t>6297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Apothecary Prince</t>
+  </si>
+  <si>
+    <t>6335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Am the Strongest Transcendent</t>
+  </si>
+  <si>
+    <t>6676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Dang Clan’s Swordmaster Heir Just Wants a Normal Life</t>
+  </si>
+  <si>
+    <t>6695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Necromancer Family’s Young Heir</t>
+  </si>
+  <si>
+    <t>7413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limit-Breaking Genius Mage</t>
+  </si>
+  <si>
+    <t>8697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 999 Goblin</t>
+  </si>
+  <si>
+    <t>level-999-goblin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Childhood Friend of the Zenith</t>
+  </si>
+  <si>
+    <t>childhood-friend-of-the-zenith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myst, Might, Mayhem</t>
+  </si>
+  <si>
+    <t>myst-might-mayhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Max-Level Player's 100th Regression</t>
+  </si>
+  <si>
+    <t>the-max-level-players-100th-regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Nebula's Civilization</t>
+  </si>
+  <si>
+    <t>the-nebulas-civilization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Sword Sense</t>
+  </si>
+  <si>
+    <t>absolute-sword-sense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worthless Regression</t>
+  </si>
+  <si>
+    <t>worthless-regression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reborn As The Heavenly Demon</t>
+  </si>
+  <si>
+    <t>reborn-as-the-heavenly-demon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavenly Grand Archive's Young Master</t>
+  </si>
+  <si>
+    <t>heavenly-grand-archives-young-master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Illegitimate Who Devours Weapons</t>
+  </si>
+  <si>
+    <t>the-illegitimate-who-devours-weapons</t>
+  </si>
+  <si>
+    <t>title</t>
   </si>
   <si>
     <t>result</t>
-  </si>
-  <si>
-    <t>completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academy's Genius Swordmaster</t>
-  </si>
-  <si>
-    <t>academys-genius-swordmaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academy's Genius Swordsman</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>asura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damn Reincarnation</t>
-  </si>
-  <si>
-    <t>damn-reincarnation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragon-Devouring Mage</t>
-  </si>
-  <si>
-    <t>dragon-devouring-mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duke Pendragon</t>
-  </si>
-  <si>
-    <t>duke-pendragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dungeon Odyssey</t>
-  </si>
-  <si>
-    <t>dungeon-odyssey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helmut: The Forsaken Child</t>
-  </si>
-  <si>
-    <t>helmut-the-forsaken-child</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinite Mage</t>
-  </si>
-  <si>
-    <t>infinite-mage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logging 10,000 Years into the Future</t>
-  </si>
-  <si>
-    <t>logging-10000-years-into-the-future</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martial God Regressed to Level 2</t>
-  </si>
-  <si>
-    <t>martial-god-regressed-to-level-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The God of War Who Regressed to Level 2</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murim Login</t>
-  </si>
-  <si>
-    <t>murim-login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nano Machine</t>
-  </si>
-  <si>
-    <t>nano-machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necromancer's Evolutionary Traits</t>
-  </si>
-  <si>
-    <t>necromancers-evolutionary-traits</t>
-  </si>
-  <si>
-    <t>Overgeared</t>
-  </si>
-  <si>
-    <t>overgeared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overpowered Sword</t>
-  </si>
-  <si>
-    <t>overpowered-sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick Me Up, Infinite Gacha</t>
-  </si>
-  <si>
-    <t>pick-me-up-infinite-gacha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player Who Can't Level Up</t>
-  </si>
-  <si>
-    <t>player-who-cant-level-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player Who Returned 10,000 Years Later</t>
-  </si>
-  <si>
-    <t>player-who-returned-10000-years-later</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the Disaster-Class Hero</t>
-  </si>
-  <si>
-    <t>return-of-the-disaster-class-hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Of The Shattered Constellation</t>
-  </si>
-  <si>
-    <t>return-of-the-shattered-constellation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the Broken Constellation</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenge of the Iron-Blooded Sword Hound</t>
-  </si>
-  <si>
-    <t>revenge-of-the-iron-blooded-sword-hound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Leveling: Ragnarok</t>
-  </si>
-  <si>
-    <t>solo-leveling-ragnarok</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Max-Level Newbie</t>
-  </si>
-  <si>
-    <t>solo-max-level-newbie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard of Reincarnation</t>
-  </si>
-  <si>
-    <t>standard-of-reincarnation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swordmaster’s Youngest Son</t>
-  </si>
-  <si>
-    <t>swordmasters-youngest-son</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent-Swallowing Magician</t>
-  </si>
-  <si>
-    <t>talent-swallowing-magician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Great Mage Returns After 4000 Years</t>
-  </si>
-  <si>
-    <t>the-great-mage-returns-after-4000-years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Heavenly Demon Can't Live a Normal Life</t>
-  </si>
-  <si>
-    <t>the-heavenly-demon-cant-live-a-normal-life</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Hero Returns</t>
-  </si>
-  <si>
-    <t>the-hero-returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Indomitable Martial King</t>
-  </si>
-  <si>
-    <t>the-indomitable-martial-king</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Slip of the Fist King</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Player Hides His Past</t>
-  </si>
-  <si>
-    <t>the-player-hides-his-past</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tutorial is Too Hard</t>
-  </si>
-  <si>
-    <t>the-tutorial-is-too-hard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wandering Warrior of Wudang</t>
-  </si>
-  <si>
-    <t>wandering-warrior-of-wudang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youngest Scion of the Mages</t>
-  </si>
-  <si>
-    <t>youngest-scion-of-the-mages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your Talent is Mine</t>
-  </si>
-  <si>
-    <t>your-talent-is-mine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BJ Archmage</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>flame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dungeon Reset</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRL Quest</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Job Change: I'm Stuck As the Weakest Dragon Tamer?!</t>
-  </si>
-  <si>
-    <t>323478</t>
-  </si>
-  <si>
-    <t>tapas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leveling with the Gods</t>
-  </si>
-  <si>
-    <t>152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leveling up with Gods</t>
-  </si>
-  <si>
-    <t>leveling-up-with-gods</t>
-  </si>
-  <si>
-    <t>vortex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressing as the Reincarnated Bastard of the Sword Clan</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>regressing-as-the-reincarnated-bastard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of The Frozen Player</t>
-  </si>
-  <si>
-    <t>153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Frozen Player Returns</t>
-  </si>
-  <si>
-    <t>the-frozen-player-returns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evolution: Road to Space Monster</t>
-  </si>
-  <si>
-    <t>evolution-road-to-space-monster-m3jhpw3j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Became a Renowned Family’s Sword Prodigy</t>
-  </si>
-  <si>
-    <t>i-became-a-renowned-family's-sword-prodigy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kill The Dragon</t>
-  </si>
-  <si>
-    <t>kill-the-dragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maxed Out Leveling</t>
-  </si>
-  <si>
-    <t>maxed-out-leveling2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranker's Return</t>
-  </si>
-  <si>
-    <t>rankers-return-c6f3k3os</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latna Saga: Survival of a Sword King</t>
-  </si>
-  <si>
-    <t>193936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Survival Story of a Sword King in a Fantasy World</t>
-  </si>
-  <si>
-    <t>survival-story-of-a-sword-king-in-a-fantasy-world</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Beginning After the End</t>
-  </si>
-  <si>
-    <t>the-beginning-after-the-end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Druid of Seoul Station</t>
-  </si>
-  <si>
-    <t>the-druid-of-seoul-station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Lord of Coins</t>
-  </si>
-  <si>
-    <t>the-lord-of-coins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Skeleton Soldier Failed to Defend the Dungeon</t>
-  </si>
-  <si>
-    <t>the-skeleton-soldier-failed-to-defend-the-dungeon-0ky1nyb0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Worn and Torn Newbie</t>
-  </si>
-  <si>
-    <t>the-worn-and-torn-newbie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zig the Blacksmith</t>
-  </si>
-  <si>
-    <t>zig-the-blacksmith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute Regression</t>
-  </si>
-  <si>
-    <t>absolute-regression</t>
-  </si>
-  <si>
-    <t>7004</t>
-  </si>
-  <si>
-    <t>webtoon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academy's Undercover Professor</t>
-  </si>
-  <si>
-    <t>academys-undercover-professor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Academy's Undercover Professor</t>
-  </si>
-  <si>
-    <t>4636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bad Born Blood</t>
-  </si>
-  <si>
-    <t>bad-born-blood</t>
-  </si>
-  <si>
-    <t>7208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boundless Necromancer</t>
-  </si>
-  <si>
-    <t>boundless-necromancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boundless Ascension</t>
-  </si>
-  <si>
-    <t>5228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eternally Regressing Knight</t>
-  </si>
-  <si>
-    <t>eternally-regressing-knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Knight Only Lives Today</t>
-  </si>
-  <si>
-    <t>6672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genius of the Unique Lineage</t>
-  </si>
-  <si>
-    <t>genius-of-the-unique-lineage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Perfect Hybrid</t>
-  </si>
-  <si>
-    <t>5050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Obtained a Mythic Item</t>
-  </si>
-  <si>
-    <t>i-obtained-a-mythic-item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mythic Item Obtained</t>
-  </si>
-  <si>
-    <t>4582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Omniscient Reader’s Viewpoint</t>
-  </si>
-  <si>
-    <t>omniscient-readers-viewpoint</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Omniscient Reader</t>
-  </si>
-  <si>
-    <t>2154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reformation of the Deadbeat Noble</t>
-  </si>
-  <si>
-    <t>reformation-of-the-deadbeat-noble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Lazy Lord Masters the Sword</t>
-  </si>
-  <si>
-    <t>3349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regressing with the King’s Power</t>
-  </si>
-  <si>
-    <t>regressing-with-the-kings-power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Returned by the King</t>
-  </si>
-  <si>
-    <t>6213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reincarnation of the Suicidal Battle God</t>
-  </si>
-  <si>
-    <t>reincarnation-of-the-suicidal-battle-god</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doom Breaker</t>
-  </si>
-  <si>
-    <t>3197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the Mount Hua Sect</t>
-  </si>
-  <si>
-    <t>return-of-the-mount-hua-sect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return of the Blossoming Blade</t>
-  </si>
-  <si>
-    <t>2849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star Instructor, Master Baek</t>
-  </si>
-  <si>
-    <t>star-instructor-master-baek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best Teacher Baek</t>
-  </si>
-  <si>
-    <t>4153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star-Embracing Swordmaster</t>
-  </si>
-  <si>
-    <t>star-embracing-swordmaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star-Fostered Swordmaster</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Stellar Swordmaster</t>
-  </si>
-  <si>
-    <t>5988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel-Eating Player</t>
-  </si>
-  <si>
-    <t>steel-eating-player</t>
-  </si>
-  <si>
-    <t>5966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surviving the Game as a Barbarian</t>
-  </si>
-  <si>
-    <t>surviving-the-game-as-a-barbarian</t>
-  </si>
-  <si>
-    <t>5515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sword Fanatic Wanders Through The Night</t>
-  </si>
-  <si>
-    <t>sword-fanatic-wanders-through-the-night</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In the Night Consumed by Blades, I Walk</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Dance of Swords in the Night</t>
-  </si>
-  <si>
-    <t>4596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Dark Magician Transmigrates After 66666 Years</t>
-  </si>
-  <si>
-    <t>the-dark-magician-transmigrates-after-66666-years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66,666 Years: Advent of the Dark Mage</t>
-  </si>
-  <si>
-    <t>3441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Extra’s Academy Survival Guide</t>
-  </si>
-  <si>
-    <t>the-extras-academy-survival-guide</t>
-  </si>
-  <si>
-    <t>6465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Greatest Estate Developer</t>
-  </si>
-  <si>
-    <t>the-greatest-estate-developer</t>
-  </si>
-  <si>
-    <t>3596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Regressed Son of a Duke is an Assassin</t>
-  </si>
-  <si>
-    <t>the-regressed-son-of-a-duke-is-an-assassin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Regressed Youngest Son of the Duke is an Assassin</t>
-  </si>
-  <si>
-    <t>133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reborn Young Lord is an Assassin</t>
-  </si>
-  <si>
-    <t>6107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villain to Kill</t>
-  </si>
-  <si>
-    <t>villain-to-kill</t>
-  </si>
-  <si>
-    <t>2857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavenly Demon Cultivation Simulation</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murim RPG Simulation</t>
-  </si>
-  <si>
-    <t>murim-rpg-simulation-jdjd0y0v</t>
-  </si>
-  <si>
-    <t>3779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jungle Juice</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>jungle-juice</t>
-  </si>
-  <si>
-    <t>2480</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solo Necromancy</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Lone Necromancer</t>
-  </si>
-  <si>
-    <t>3690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Dungeon Cleaning Life of a Once Genius Hunter</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>4677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster Eater</t>
-  </si>
-  <si>
-    <t>monster-eater</t>
-  </si>
-  <si>
-    <t>7363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regression of the Close Combat Mage</t>
-  </si>
-  <si>
-    <t>regression-of-the-close-combat-mage</t>
-  </si>
-  <si>
-    <t>6780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return to Player</t>
-  </si>
-  <si>
-    <t>return-to-player</t>
-  </si>
-  <si>
-    <t>2574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower of God: Urek Mazino</t>
-  </si>
-  <si>
-    <t>tog-urek-mazino</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower of God</t>
-  </si>
-  <si>
-    <t>Eleceed</t>
-  </si>
-  <si>
-    <t>1571</t>
-  </si>
-  <si>
-    <t>Deor</t>
-  </si>
-  <si>
-    <t>1663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My S-Class Hunters</t>
-  </si>
-  <si>
-    <t>3963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Was the Final Boss</t>
-  </si>
-  <si>
-    <t>5170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lord of Goblins</t>
-  </si>
-  <si>
-    <t>5227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Hammer</t>
-  </si>
-  <si>
-    <t>5382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enrolling in the Transcendent Academy</t>
-  </si>
-  <si>
-    <t>5420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becoming the Monarch</t>
-  </si>
-  <si>
-    <t>5549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time-Limited Genius Dark Knight</t>
-  </si>
-  <si>
-    <t>5639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Night of the Goblin</t>
-  </si>
-  <si>
-    <t>5986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Last Adventurer</t>
-  </si>
-  <si>
-    <t>6135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supremely Talented Player</t>
-  </si>
-  <si>
-    <t>6215</t>
-  </si>
-  <si>
-    <t>Reincarnator</t>
-  </si>
-  <si>
-    <t>6297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Apothecary Prince</t>
-  </si>
-  <si>
-    <t>6335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I Am the Strongest Transcendent</t>
-  </si>
-  <si>
-    <t>6676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Dang Clan’s Swordmaster Heir Just Wants a Normal Life</t>
-  </si>
-  <si>
-    <t>6695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Necromancer Family’s Young Heir</t>
-  </si>
-  <si>
-    <t>7413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limit-Breaking Genius Mage</t>
-  </si>
-  <si>
-    <t>8697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 999 Goblin</t>
-  </si>
-  <si>
-    <t>level-999-goblin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Childhood Friend of the Zenith</t>
-  </si>
-  <si>
-    <t>childhood-friend-of-the-zenith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myst, Might, Mayhem</t>
-  </si>
-  <si>
-    <t>myst-might-mayhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Max-Level Player's 100th Regression</t>
-  </si>
-  <si>
-    <t>the-max-level-players-100th-regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Nebula's Civilization</t>
-  </si>
-  <si>
-    <t>the-nebulas-civilization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute Sword Sense</t>
-  </si>
-  <si>
-    <t>absolute-sword-sense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worthless Regression</t>
-  </si>
-  <si>
-    <t>worthless-regression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reborn As The Heavenly Demon</t>
-  </si>
-  <si>
-    <t>reborn-as-the-heavenly-demon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavenly Grand Archive's Young Master</t>
-  </si>
-  <si>
-    <t>heavenly-grand-archives-young-master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Illegitimate Who Devours Weapons</t>
-  </si>
-  <si>
-    <t>the-illegitimate-who-devours-weapons</t>
-  </si>
-  <si>
-    <t>title</t>
   </si>
   <si>
     <t>id</t>
@@ -1098,11 +1101,12 @@
     <xf fontId="1" fillId="5" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="1" fillId="6" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="3" borderId="0" numFmtId="0" xfId="2" applyFont="1" applyFill="1">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -2599,7 +2603,7 @@
       <c r="I55" t="s">
         <v>138</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="2" t="s">
         <v>140</v>
       </c>
       <c r="K55" t="s">
@@ -2620,7 +2624,7 @@
       <c r="I56" t="s">
         <v>144</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="2" t="s">
         <v>145</v>
       </c>
       <c r="K56" t="s">
@@ -2641,7 +2645,7 @@
       <c r="I57" t="s">
         <v>146</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="2" t="s">
         <v>148</v>
       </c>
       <c r="K57" t="s">
@@ -2662,7 +2666,7 @@
       <c r="I58" t="s">
         <v>151</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="2" t="s">
         <v>152</v>
       </c>
       <c r="K58" t="s">
@@ -2683,7 +2687,7 @@
       <c r="I59" t="s">
         <v>155</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="2" t="s">
         <v>156</v>
       </c>
       <c r="K59" t="s">
@@ -2704,7 +2708,7 @@
       <c r="I60" t="s">
         <v>159</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="2" t="s">
         <v>160</v>
       </c>
       <c r="K60" t="s">
@@ -2725,7 +2729,7 @@
       <c r="I61" t="s">
         <v>163</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="2" t="s">
         <v>164</v>
       </c>
       <c r="K61" t="s">
@@ -2752,7 +2756,7 @@
       <c r="I62" t="s">
         <v>168</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="2" t="s">
         <v>169</v>
       </c>
       <c r="K62" t="s">
@@ -2773,7 +2777,7 @@
       <c r="I63" t="s">
         <v>172</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="2" t="s">
         <v>173</v>
       </c>
       <c r="K63" t="s">
@@ -2794,7 +2798,7 @@
       <c r="I64" t="s">
         <v>176</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" s="2" t="s">
         <v>177</v>
       </c>
       <c r="K64" t="s">
@@ -2815,7 +2819,7 @@
       <c r="I65" t="s">
         <v>180</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" s="2" t="s">
         <v>181</v>
       </c>
       <c r="K65" t="s">
@@ -2836,7 +2840,7 @@
       <c r="I66" t="s">
         <v>184</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="2" t="s">
         <v>185</v>
       </c>
       <c r="K66" t="s">
@@ -2857,7 +2861,7 @@
       <c r="I67" t="s">
         <v>188</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="2" t="s">
         <v>189</v>
       </c>
       <c r="K67" t="s">
@@ -2884,7 +2888,7 @@
       <c r="I68" t="s">
         <v>194</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="2" t="s">
         <v>195</v>
       </c>
       <c r="K68" t="s">
@@ -2905,7 +2909,7 @@
       <c r="I69" t="s">
         <v>196</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="2" t="s">
         <v>198</v>
       </c>
       <c r="K69" t="s">
@@ -2926,7 +2930,7 @@
       <c r="I70" t="s">
         <v>199</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="2" t="s">
         <v>201</v>
       </c>
       <c r="K70" t="s">
@@ -2953,7 +2957,7 @@
       <c r="I71" t="s">
         <v>206</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="2" t="s">
         <v>207</v>
       </c>
       <c r="K71" t="s">
@@ -2974,7 +2978,7 @@
       <c r="I72" t="s">
         <v>210</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J72" s="2" t="s">
         <v>211</v>
       </c>
       <c r="K72" t="s">
@@ -2995,7 +2999,7 @@
       <c r="I73" t="s">
         <v>212</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J73" s="2" t="s">
         <v>214</v>
       </c>
       <c r="K73" t="s">
@@ -3016,15 +3020,15 @@
       <c r="I74" t="s">
         <v>215</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J74" s="2" t="s">
         <v>217</v>
       </c>
       <c r="K74" t="s">
         <v>141</v>
       </c>
       <c r="L74" s="1" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>TRUE</f>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -3043,7 +3047,7 @@
       <c r="I75" t="s">
         <v>222</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J75" s="2" t="s">
         <v>223</v>
       </c>
       <c r="K75" t="s">
@@ -3064,7 +3068,7 @@
       <c r="I76" t="s">
         <v>224</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J76" s="2" t="s">
         <v>226</v>
       </c>
       <c r="K76" t="s">
@@ -3091,7 +3095,7 @@
       <c r="I77" t="s">
         <v>229</v>
       </c>
-      <c r="J77" t="s">
+      <c r="J77" s="2" t="s">
         <v>231</v>
       </c>
       <c r="K77" t="s">
@@ -3115,7 +3119,7 @@
       <c r="I78" t="s">
         <v>232</v>
       </c>
-      <c r="J78" t="s">
+      <c r="J78" s="2" t="s">
         <v>235</v>
       </c>
       <c r="K78" t="s">
@@ -3136,7 +3140,7 @@
       <c r="I79" t="s">
         <v>238</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J79" s="2" t="s">
         <v>239</v>
       </c>
       <c r="K79" t="s">
@@ -3157,7 +3161,7 @@
       <c r="I80" t="s">
         <v>240</v>
       </c>
-      <c r="J80" t="s">
+      <c r="J80" s="2" t="s">
         <v>242</v>
       </c>
       <c r="K80" t="s">
@@ -3178,7 +3182,7 @@
       <c r="I81" t="s">
         <v>243</v>
       </c>
-      <c r="J81" t="s">
+      <c r="J81" s="2" t="s">
         <v>245</v>
       </c>
       <c r="K81" t="s">
@@ -3199,7 +3203,7 @@
       <c r="I82" t="s">
         <v>246</v>
       </c>
-      <c r="J82" t="s">
+      <c r="J82" s="2" t="s">
         <v>248</v>
       </c>
       <c r="K82" t="s">
@@ -3220,7 +3224,7 @@
       <c r="I83" t="s">
         <v>249</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J83" s="2" t="s">
         <v>251</v>
       </c>
       <c r="K83" t="s">
@@ -3241,7 +3245,7 @@
       <c r="I84" t="s">
         <v>252</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J84" s="2" t="s">
         <v>254</v>
       </c>
       <c r="K84" t="s">
@@ -3256,7 +3260,7 @@
       <c r="I85" t="s">
         <v>255</v>
       </c>
-      <c r="J85" t="s">
+      <c r="J85" s="2" t="s">
         <v>205</v>
       </c>
       <c r="K85" t="s">
@@ -3271,7 +3275,7 @@
       <c r="I86" t="s">
         <v>256</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J86" s="2" t="s">
         <v>257</v>
       </c>
       <c r="K86" t="s">
@@ -3286,7 +3290,7 @@
       <c r="I87" t="s">
         <v>258</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J87" s="2" t="s">
         <v>259</v>
       </c>
       <c r="K87" t="s">
@@ -3301,14 +3305,14 @@
       <c r="I88" t="s">
         <v>260</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J88" s="2" t="s">
         <v>261</v>
       </c>
       <c r="K88" t="s">
         <v>141</v>
       </c>
       <c r="L88" s="1" t="b">
-        <f t="shared" ref="L88:L105" si="3">FALSE</f>
+        <f t="shared" ref="L88:L113" si="3">FALSE</f>
         <v>0</v>
       </c>
     </row>
@@ -3316,7 +3320,7 @@
       <c r="I89" t="s">
         <v>262</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J89" s="2" t="s">
         <v>263</v>
       </c>
       <c r="K89" t="s">
@@ -3331,7 +3335,7 @@
       <c r="I90" t="s">
         <v>264</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J90" s="2" t="s">
         <v>265</v>
       </c>
       <c r="K90" t="s">
@@ -3346,7 +3350,7 @@
       <c r="I91" t="s">
         <v>266</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J91" s="2" t="s">
         <v>267</v>
       </c>
       <c r="K91" t="s">
@@ -3361,7 +3365,7 @@
       <c r="I92" t="s">
         <v>268</v>
       </c>
-      <c r="J92" t="s">
+      <c r="J92" s="2" t="s">
         <v>269</v>
       </c>
       <c r="K92" t="s">
@@ -3376,7 +3380,7 @@
       <c r="I93" t="s">
         <v>270</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J93" s="2" t="s">
         <v>271</v>
       </c>
       <c r="K93" t="s">
@@ -3391,7 +3395,7 @@
       <c r="I94" t="s">
         <v>272</v>
       </c>
-      <c r="J94" t="s">
+      <c r="J94" s="2" t="s">
         <v>273</v>
       </c>
       <c r="K94" t="s">
@@ -3406,7 +3410,7 @@
       <c r="I95" t="s">
         <v>274</v>
       </c>
-      <c r="J95" t="s">
+      <c r="J95" s="2" t="s">
         <v>275</v>
       </c>
       <c r="K95" t="s">
@@ -3421,7 +3425,7 @@
       <c r="I96" t="s">
         <v>276</v>
       </c>
-      <c r="J96" t="s">
+      <c r="J96" s="2" t="s">
         <v>277</v>
       </c>
       <c r="K96" t="s">
@@ -3436,7 +3440,7 @@
       <c r="I97" t="s">
         <v>278</v>
       </c>
-      <c r="J97" t="s">
+      <c r="J97" s="2" t="s">
         <v>279</v>
       </c>
       <c r="K97" t="s">
@@ -3451,7 +3455,7 @@
       <c r="I98" t="s">
         <v>280</v>
       </c>
-      <c r="J98" t="s">
+      <c r="J98" s="2" t="s">
         <v>281</v>
       </c>
       <c r="K98" t="s">
@@ -3466,7 +3470,7 @@
       <c r="I99" t="s">
         <v>282</v>
       </c>
-      <c r="J99" t="s">
+      <c r="J99" s="2" t="s">
         <v>283</v>
       </c>
       <c r="K99" t="s">
@@ -3481,7 +3485,7 @@
       <c r="I100" t="s">
         <v>284</v>
       </c>
-      <c r="J100" t="s">
+      <c r="J100" s="2" t="s">
         <v>285</v>
       </c>
       <c r="K100" t="s">
@@ -3496,7 +3500,7 @@
       <c r="I101" t="s">
         <v>286</v>
       </c>
-      <c r="J101" t="s">
+      <c r="J101" s="2" t="s">
         <v>287</v>
       </c>
       <c r="K101" t="s">
@@ -3511,7 +3515,7 @@
       <c r="I102" t="s">
         <v>288</v>
       </c>
-      <c r="J102" t="s">
+      <c r="J102" s="2" t="s">
         <v>289</v>
       </c>
       <c r="K102" t="s">
@@ -3526,7 +3530,7 @@
       <c r="I103" t="s">
         <v>290</v>
       </c>
-      <c r="J103" t="s">
+      <c r="J103" s="2" t="s">
         <v>291</v>
       </c>
       <c r="K103" t="s">
@@ -3578,7 +3582,7 @@
         <v>16</v>
       </c>
       <c r="L106" t="b">
-        <f>FALSE</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3593,7 +3597,7 @@
         <v>16</v>
       </c>
       <c r="L107" t="b">
-        <f>FALSE</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3608,7 +3612,7 @@
         <v>16</v>
       </c>
       <c r="L108" t="b">
-        <f>FALSE</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3623,7 +3627,7 @@
         <v>16</v>
       </c>
       <c r="L109" t="b">
-        <f>FALSE</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3638,7 +3642,7 @@
         <v>16</v>
       </c>
       <c r="L110" t="b">
-        <f>FALSE</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3653,7 +3657,7 @@
         <v>16</v>
       </c>
       <c r="L111" t="b">
-        <f>FALSE</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3668,7 +3672,7 @@
         <v>16</v>
       </c>
       <c r="L112" t="b">
-        <f>FALSE</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3683,7 +3687,7 @@
         <v>16</v>
       </c>
       <c r="L113" t="b">
-        <f>FALSE</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3710,1244 +3714,1244 @@
         <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>313</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="b">
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="b">
         <f t="shared" ref="C2:C4" si="4">FALSE</f>
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3" t="b">
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="b">
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="b">
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="b">
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="b">
         <f t="shared" ref="C6:C62" si="5">FALSE</f>
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="3" t="b">
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3" t="b">
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="3" t="b">
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="3" t="b">
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="3" t="b">
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3" t="b">
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="3" t="b">
+      <c r="B13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="3" t="b">
+      <c r="B14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="3" t="b">
+      <c r="B15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="3" t="b">
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="3" t="b">
+      <c r="B17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="3" t="b">
+      <c r="B18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="3" t="b">
+      <c r="B19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="3" t="b">
+      <c r="B20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="3" t="b">
+      <c r="B21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="3" t="b">
+      <c r="B22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="3" t="b">
+      <c r="B23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" s="3" t="b">
+      <c r="B24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="3" t="b">
+      <c r="B25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="3" t="b">
+      <c r="B26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="3" t="b">
+      <c r="B27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="3" t="b">
+      <c r="B28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="3" t="b">
+      <c r="B29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="3" t="b">
+      <c r="B30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="3" t="b">
+      <c r="B31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="3" t="b">
+      <c r="B32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" s="3" t="b">
+      <c r="B33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" s="3" t="b">
+      <c r="B34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="3" t="b">
+      <c r="B35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="3" t="b">
+      <c r="B36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="4" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C37" s="4" t="b">
+      <c r="C37" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="4" t="b">
+      <c r="C38" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C39" s="4" t="b">
+      <c r="C39" s="5" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="5" t="b">
+      <c r="C40" s="6" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="5" t="b">
+      <c r="C41" s="6" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C42" s="6" t="b">
+      <c r="C42" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C43" s="6" t="b">
+      <c r="C43" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="6" t="b">
+      <c r="C44" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="6" t="b">
+      <c r="C45" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="6" t="b">
+      <c r="C46" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="6" t="b">
+      <c r="C47" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="6" t="b">
+      <c r="C48" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="6" t="b">
+      <c r="C49" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="6" t="b">
+      <c r="C50" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="6" t="b">
+      <c r="C51" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C52" s="6" t="b">
+      <c r="C52" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C53" s="6" t="b">
+      <c r="C53" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="6" t="b">
+      <c r="C54" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="6" t="b">
+      <c r="C55" s="7" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B56" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" s="7" t="b">
+      <c r="B56" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" s="8" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C57" s="7" t="b">
+      <c r="B57" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" s="8" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C58" s="7" t="b">
+      <c r="B58" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="8" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C59" s="7" t="b">
+      <c r="B59" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C59" s="8" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C60" s="7" t="b">
+      <c r="B60" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C60" s="8" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C61" s="7" t="b">
+      <c r="B61" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="8" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C62" s="7" t="b">
+      <c r="B62" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="8" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C63" s="8" t="b">
+      <c r="B63" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" s="9" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B64" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="7" t="b">
+      <c r="B64" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="8" t="b">
         <f t="shared" ref="C64:C104" si="6">FALSE</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="B65" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C65" s="7" t="b">
+      <c r="B65" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B66" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C66" s="7" t="b">
+      <c r="B66" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="B67" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C67" s="7" t="b">
+      <c r="B67" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C68" s="7" t="b">
+      <c r="B68" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C68" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C69" s="7" t="b">
+      <c r="B69" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C69" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="B70" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C70" s="7" t="b">
+      <c r="B70" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C71" s="7" t="b">
+      <c r="B71" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C71" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C72" s="7" t="b">
+      <c r="B72" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C72" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C73" s="7" t="b">
+      <c r="B73" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C74" s="7" t="b">
+      <c r="B74" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B75" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C75" s="7" t="b">
+      <c r="B75" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C76" s="7" t="b">
+      <c r="B76" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C77" s="7" t="b">
+      <c r="B77" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C78" s="7" t="b">
+      <c r="B78" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="B79" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C79" s="7" t="b">
+      <c r="B79" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B80" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C80" s="7" t="b">
+      <c r="B80" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C80" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="B81" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C81" s="7" t="b">
+      <c r="B81" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C81" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="s">
+      <c r="A82" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B82" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C82" s="7" t="b">
+      <c r="B82" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C82" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="s">
+      <c r="A83" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C83" s="7" t="b">
+      <c r="B83" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C83" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C84" s="7" t="b">
+      <c r="B84" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C84" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="s">
+      <c r="A85" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C85" s="7" t="b">
+      <c r="B85" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C85" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="s">
+      <c r="A86" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B86" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C86" s="7" t="b">
+      <c r="B86" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C86" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C87" s="7" t="b">
+      <c r="B87" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C87" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="B88" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C88" s="7" t="b">
+      <c r="B88" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C88" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="B89" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C89" s="7" t="b">
+      <c r="B89" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C89" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="s">
+      <c r="A90" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B90" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C90" s="7" t="b">
+      <c r="B90" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C90" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B91" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C91" s="7" t="b">
+      <c r="B91" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C91" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="B92" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C92" s="7" t="b">
+      <c r="B92" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C92" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B93" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C93" s="7" t="b">
+      <c r="B93" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C93" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="B94" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C94" s="7" t="b">
+      <c r="B94" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C94" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B95" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C95" s="7" t="b">
+      <c r="B95" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C95" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="B96" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C96" s="7" t="b">
+      <c r="B96" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C96" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="B97" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C97" s="7" t="b">
+      <c r="B97" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C97" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="7" t="s">
+      <c r="A98" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B98" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C98" s="7" t="b">
+      <c r="B98" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C98" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="s">
+      <c r="A99" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="B99" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C99" s="7" t="b">
+      <c r="B99" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C99" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="s">
+      <c r="A100" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B100" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C100" s="7" t="b">
+      <c r="B100" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C100" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C101" s="7" t="b">
+      <c r="B101" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C101" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="s">
+      <c r="A102" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="B102" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C102" s="7" t="b">
+      <c r="B102" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C102" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="7" t="s">
+      <c r="A103" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="B103" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C103" s="7" t="b">
+      <c r="B103" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C103" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="s">
+      <c r="A104" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B104" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C104" s="7" t="b">
+      <c r="B104" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C104" s="8" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -4978,7 +4982,7 @@
         <v>312</v>
       </c>
       <c r="B1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2">
@@ -5010,7 +5014,7 @@
         <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" ht="16.5">
@@ -5059,7 +5063,7 @@
         <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -5723,47 +5727,47 @@
         <v>312</v>
       </c>
       <c r="B1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -5787,7 +5791,7 @@
         <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" ht="16.5">
@@ -5923,7 +5927,7 @@
         <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" ht="16.5">
